--- a/research/traditional_assets/database/data/jamaica/jamaica_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/jamaica/jamaica_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ9"/>
+  <dimension ref="A1:AQ10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.114</v>
+        <v>0.206</v>
       </c>
       <c r="E2">
-        <v>0.16</v>
+        <v>0.103855</v>
       </c>
       <c r="G2">
-        <v>0.070057523463518</v>
+        <v>0.04601701469450889</v>
       </c>
       <c r="H2">
-        <v>0.06963366636391159</v>
+        <v>0.04601701469450889</v>
       </c>
       <c r="I2">
-        <v>0.07462912503784437</v>
+        <v>0.04949729311678268</v>
       </c>
       <c r="J2">
-        <v>0.06372228738584451</v>
+        <v>0.04176973318673211</v>
       </c>
       <c r="K2">
-        <v>19.314</v>
+        <v>38.522</v>
       </c>
       <c r="L2">
-        <v>0.2923705722070845</v>
+        <v>0.3724091260634184</v>
       </c>
       <c r="M2">
-        <v>5.9472</v>
+        <v>11.175</v>
       </c>
       <c r="N2">
-        <v>0.01903835072667904</v>
+        <v>0.03448541891683381</v>
       </c>
       <c r="O2">
-        <v>0.3079217148182665</v>
+        <v>0.2900939722755828</v>
       </c>
       <c r="P2">
-        <v>5.9472</v>
+        <v>11.175</v>
       </c>
       <c r="Q2">
-        <v>0.01903835072667904</v>
+        <v>0.03448541891683381</v>
       </c>
       <c r="R2">
-        <v>0.3079217148182665</v>
+        <v>0.2900939722755828</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,70 +636,70 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>41.374</v>
+        <v>45.795</v>
       </c>
       <c r="V2">
-        <v>0.1324476599014021</v>
+        <v>0.1413207838296559</v>
       </c>
       <c r="W2">
-        <v>0.1617283950617284</v>
+        <v>0.1707854154213987</v>
       </c>
       <c r="X2">
-        <v>0.0422012243367937</v>
+        <v>0.07825883892266655</v>
       </c>
       <c r="Y2">
-        <v>0.1195271707249347</v>
+        <v>0.09252657649873214</v>
       </c>
       <c r="Z2">
-        <v>0.166677600205887</v>
+        <v>0.2052018591954992</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.04751435795120395</v>
+        <v>0.08506621525715261</v>
       </c>
       <c r="AC2">
-        <v>-0.04751435795120395</v>
+        <v>-0.08506621525715261</v>
       </c>
       <c r="AD2">
-        <v>328.96</v>
+        <v>365.87</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>328.96</v>
+        <v>365.87</v>
       </c>
       <c r="AG2">
-        <v>287.586</v>
+        <v>320.075</v>
       </c>
       <c r="AH2">
-        <v>0.5129260610596563</v>
+        <v>0.530307861781076</v>
       </c>
       <c r="AI2">
-        <v>0.6066910110287338</v>
+        <v>0.5468091466148558</v>
       </c>
       <c r="AJ2">
-        <v>0.4793371624392049</v>
+        <v>0.4969144187851737</v>
       </c>
       <c r="AK2">
-        <v>0.5742004528338053</v>
+        <v>0.5135126462967567</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.277</v>
+        <v>-0.184</v>
       </c>
       <c r="AN2">
-        <v>63.62862669245649</v>
+        <v>67.62846580406654</v>
       </c>
       <c r="AP2">
-        <v>55.62591876208898</v>
+        <v>59.16358595194085</v>
       </c>
       <c r="AQ2">
-        <v>-17.79783393501805</v>
+        <v>-27.82608695652174</v>
       </c>
     </row>
     <row r="3">
@@ -719,46 +719,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.174</v>
+        <v>0.206</v>
       </c>
       <c r="E3">
-        <v>0.16</v>
+        <v>0.257</v>
       </c>
       <c r="G3">
-        <v>0.3593749999999999</v>
+        <v>0.344927536231884</v>
       </c>
       <c r="H3">
-        <v>0.3593749999999999</v>
+        <v>0.344927536231884</v>
       </c>
       <c r="I3">
-        <v>0.38515625</v>
+        <v>0.3710144927536232</v>
       </c>
       <c r="J3">
-        <v>0.2645517676767676</v>
+        <v>0.2480417041949835</v>
       </c>
       <c r="K3">
-        <v>3.41</v>
+        <v>3.54</v>
       </c>
       <c r="L3">
-        <v>0.26640625</v>
+        <v>0.2565217391304347</v>
       </c>
       <c r="M3">
-        <v>1.31</v>
+        <v>2.01</v>
       </c>
       <c r="N3">
-        <v>0.01589805825242718</v>
+        <v>0.02742155525238745</v>
       </c>
       <c r="O3">
-        <v>0.3841642228739003</v>
+        <v>0.5677966101694915</v>
       </c>
       <c r="P3">
-        <v>1.31</v>
+        <v>2.01</v>
       </c>
       <c r="Q3">
-        <v>0.01589805825242718</v>
+        <v>0.02742155525238745</v>
       </c>
       <c r="R3">
-        <v>0.3841642228739003</v>
+        <v>0.5677966101694915</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -767,31 +767,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.926</v>
+        <v>0.37</v>
       </c>
       <c r="V3">
-        <v>0.0112378640776699</v>
+        <v>0.00504774897680764</v>
       </c>
       <c r="W3">
-        <v>0.3440968718466196</v>
+        <v>0.3025641025641026</v>
       </c>
       <c r="X3">
-        <v>0.03360415921485008</v>
+        <v>0.06311951548698429</v>
       </c>
       <c r="Y3">
-        <v>0.3104927126317695</v>
+        <v>0.2394445870771183</v>
       </c>
       <c r="Z3">
-        <v>1.396922405325767</v>
+        <v>1.280861332838315</v>
       </c>
       <c r="AA3">
-        <v>0.3695582916362137</v>
+        <v>0.3177070278346735</v>
       </c>
       <c r="AB3">
-        <v>0.03360415921485008</v>
+        <v>0.06311951548698429</v>
       </c>
       <c r="AC3">
-        <v>0.3359541324213636</v>
+        <v>0.2545875123476892</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -803,7 +803,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-0.926</v>
+        <v>-0.37</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -812,25 +812,25 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.01136558902226477</v>
+        <v>-0.005073358014534486</v>
       </c>
       <c r="AK3">
-        <v>-0.08594765175422314</v>
+        <v>-0.02929532858273951</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.277</v>
+        <v>-0.184</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-0.179110251450677</v>
+        <v>-0.06839186691312384</v>
       </c>
       <c r="AQ3">
-        <v>-17.79783393501805</v>
+        <v>-27.82608695652174</v>
       </c>
     </row>
     <row r="4">
@@ -850,10 +850,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.114</v>
+        <v>0.0394</v>
       </c>
       <c r="E4">
-        <v>0.125</v>
+        <v>0.00171</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -868,10 +868,10 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0.464</v>
+        <v>0.322</v>
       </c>
       <c r="L4">
-        <v>0.225242718446602</v>
+        <v>0.1712765957446809</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -895,55 +895,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.348</v>
+        <v>0.515</v>
       </c>
       <c r="V4">
-        <v>0.01338461538461538</v>
+        <v>0.04256198347107439</v>
       </c>
       <c r="W4">
-        <v>0.1651245551601424</v>
+        <v>0.1018987341772152</v>
       </c>
       <c r="X4">
-        <v>0.03465035590892045</v>
+        <v>0.0659383684184302</v>
       </c>
       <c r="Y4">
-        <v>0.1304741992512219</v>
+        <v>0.03596036575878499</v>
       </c>
       <c r="Z4">
-        <v>0.4429155020425715</v>
+        <v>0.393964794635373</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.03631354905798297</v>
+        <v>0.06977180252380108</v>
       </c>
       <c r="AC4">
-        <v>-0.03631354905798297</v>
+        <v>-0.06977180252380108</v>
       </c>
       <c r="AD4">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="AG4">
-        <v>1.612</v>
+        <v>1.355</v>
       </c>
       <c r="AH4">
-        <v>0.07010014306151645</v>
+        <v>0.1338582677165354</v>
       </c>
       <c r="AI4">
-        <v>0.3828125</v>
+        <v>0.3568702290076336</v>
       </c>
       <c r="AJ4">
-        <v>0.0583804143126177</v>
+        <v>0.1007060572277964</v>
       </c>
       <c r="AK4">
-        <v>0.3378038558256496</v>
+        <v>0.2867724867724868</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -969,10 +969,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.06</v>
+        <v>0.0597</v>
       </c>
       <c r="E5">
-        <v>-0.0891</v>
+        <v>-0.111</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -987,28 +987,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="L5">
-        <v>0.2543689320388349</v>
+        <v>0.2205128205128205</v>
       </c>
       <c r="M5">
-        <v>0.9</v>
+        <v>1.18</v>
       </c>
       <c r="N5">
-        <v>0.02639296187683285</v>
+        <v>0.02505307855626327</v>
       </c>
       <c r="O5">
-        <v>0.3435114503816794</v>
+        <v>0.4573643410852713</v>
       </c>
       <c r="P5">
-        <v>0.9</v>
+        <v>1.18</v>
       </c>
       <c r="Q5">
-        <v>0.02639296187683285</v>
+        <v>0.02505307855626327</v>
       </c>
       <c r="R5">
-        <v>0.3435114503816794</v>
+        <v>0.4573643410852713</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1017,55 +1017,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>2.71</v>
+        <v>4.81</v>
       </c>
       <c r="V5">
-        <v>0.07947214076246334</v>
+        <v>0.1021231422505308</v>
       </c>
       <c r="W5">
-        <v>0.1617283950617284</v>
+        <v>0.1474285714285714</v>
       </c>
       <c r="X5">
-        <v>0.04101124934044256</v>
+        <v>0.07074840808401597</v>
       </c>
       <c r="Y5">
-        <v>0.1207171457212858</v>
+        <v>0.07668016334455546</v>
       </c>
       <c r="Z5">
-        <v>0.3246139300346676</v>
+        <v>0.3546529251288269</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.04705415949048441</v>
+        <v>0.07777551842588168</v>
       </c>
       <c r="AC5">
-        <v>-0.04705415949048441</v>
+        <v>-0.07777551842588168</v>
       </c>
       <c r="AD5">
-        <v>18.2</v>
+        <v>19.7</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>18.2</v>
+        <v>19.7</v>
       </c>
       <c r="AG5">
-        <v>15.49</v>
+        <v>14.89</v>
       </c>
       <c r="AH5">
-        <v>0.3479923518164436</v>
+        <v>0.2949101796407186</v>
       </c>
       <c r="AI5">
-        <v>0.5098039215686274</v>
+        <v>0.5143603133159269</v>
       </c>
       <c r="AJ5">
-        <v>0.31236136317806</v>
+        <v>0.2402000322632683</v>
       </c>
       <c r="AK5">
-        <v>0.4695362230979085</v>
+        <v>0.4446103314422216</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1091,10 +1091,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.244</v>
+        <v>0.381</v>
       </c>
       <c r="E6">
-        <v>0.27</v>
+        <v>0.206</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1109,28 +1109,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="L6">
-        <v>0.5733333333333334</v>
+        <v>0.5</v>
       </c>
       <c r="M6">
-        <v>1.24</v>
+        <v>1.51</v>
       </c>
       <c r="N6">
-        <v>0.02743362831858407</v>
+        <v>0.03087934560327198</v>
       </c>
       <c r="O6">
-        <v>0.7209302325581396</v>
+        <v>0.9263803680981596</v>
       </c>
       <c r="P6">
-        <v>1.24</v>
+        <v>1.51</v>
       </c>
       <c r="Q6">
-        <v>0.02743362831858407</v>
+        <v>0.03087934560327198</v>
       </c>
       <c r="R6">
-        <v>0.7209302325581396</v>
+        <v>0.9263803680981596</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1139,55 +1139,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>2.87</v>
+        <v>3.62</v>
       </c>
       <c r="V6">
-        <v>0.06349557522123894</v>
+        <v>0.07402862985685071</v>
       </c>
       <c r="W6">
-        <v>0.2658423493044823</v>
+        <v>0.2328571428571428</v>
       </c>
       <c r="X6">
-        <v>0.0422012243367937</v>
+        <v>0.07337697984115711</v>
       </c>
       <c r="Y6">
-        <v>0.2236411249676886</v>
+        <v>0.1594801630159857</v>
       </c>
       <c r="Z6">
-        <v>0.1235076163030054</v>
+        <v>0.1014628073451603</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.04751435795120395</v>
+        <v>0.08100765259514765</v>
       </c>
       <c r="AC6">
-        <v>-0.04751435795120395</v>
+        <v>-0.08100765259514765</v>
       </c>
       <c r="AD6">
-        <v>28</v>
+        <v>27.5</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>28</v>
+        <v>27.5</v>
       </c>
       <c r="AG6">
-        <v>25.13</v>
+        <v>23.88</v>
       </c>
       <c r="AH6">
-        <v>0.3825136612021858</v>
+        <v>0.3599476439790575</v>
       </c>
       <c r="AI6">
-        <v>0.8</v>
+        <v>0.7980266976204294</v>
       </c>
       <c r="AJ6">
-        <v>0.3573155125835348</v>
+        <v>0.3281121187139324</v>
       </c>
       <c r="AK6">
-        <v>0.7821350762527234</v>
+        <v>0.7743190661478599</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mayberry Investments Limited (JMSE:MIL)</t>
+          <t>Sygnus Real Estate Finance Limited (JMSE:SRFJMD)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1212,104 +1212,80 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D7">
-        <v>0.07290000000000001</v>
-      </c>
-      <c r="E7">
-        <v>0.216</v>
-      </c>
-      <c r="G7">
-        <v>0.002592592592592593</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
       <c r="K7">
-        <v>5.63</v>
-      </c>
-      <c r="L7">
-        <v>0.5212962962962963</v>
+        <v>4.64</v>
       </c>
       <c r="M7">
-        <v>2.4022</v>
+        <v>-0</v>
       </c>
       <c r="N7">
-        <v>0.03831259968102073</v>
+        <v>-0</v>
       </c>
       <c r="O7">
-        <v>0.4266785079928951</v>
+        <v>-0</v>
       </c>
       <c r="P7">
-        <v>2.4022</v>
+        <v>-0</v>
       </c>
       <c r="Q7">
-        <v>0.03831259968102073</v>
+        <v>-0</v>
       </c>
       <c r="R7">
-        <v>0.4266785079928951</v>
+        <v>-0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
       <c r="U7">
-        <v>10.4</v>
+        <v>3.1</v>
       </c>
       <c r="V7">
-        <v>0.1658692185007974</v>
+        <v>0.1441860465116279</v>
       </c>
       <c r="W7">
-        <v>0.07929577464788733</v>
+        <v>0.1941422594142259</v>
       </c>
       <c r="X7">
-        <v>0.0528166116053882</v>
+        <v>0.08314069800417601</v>
       </c>
       <c r="Y7">
-        <v>0.02647916304249913</v>
+        <v>0.1110015614100499</v>
       </c>
       <c r="Z7">
-        <v>0.07654145995747698</v>
+        <v>0</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.05604458673930178</v>
+        <v>0.08912477791915754</v>
       </c>
       <c r="AC7">
-        <v>-0.05604458673930178</v>
+        <v>-0.08912477791915754</v>
       </c>
       <c r="AD7">
-        <v>86.8</v>
+        <v>23.6</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>86.8</v>
+        <v>23.6</v>
       </c>
       <c r="AG7">
-        <v>76.39999999999999</v>
+        <v>20.5</v>
       </c>
       <c r="AH7">
-        <v>0.5806020066889632</v>
+        <v>0.5232815964523282</v>
       </c>
       <c r="AI7">
-        <v>0.4054180289584307</v>
+        <v>0.3172043010752688</v>
       </c>
       <c r="AJ7">
-        <v>0.5492451473759885</v>
+        <v>0.4880952380952381</v>
       </c>
       <c r="AK7">
-        <v>0.3750613647520864</v>
+        <v>0.2875175315568023</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1326,7 +1302,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Victoria Mutual Investments Limited (JMSE:VMIL)</t>
+          <t>Mayberry Investments Limited (JMSE:MIL)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1334,6 +1310,9 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D8">
+        <v>0.596</v>
+      </c>
       <c r="G8">
         <v>0</v>
       </c>
@@ -1347,82 +1326,85 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>3.53</v>
+        <v>21.9</v>
       </c>
       <c r="L8">
-        <v>0.2385135135135135</v>
+        <v>0.4478527607361963</v>
       </c>
       <c r="M8">
-        <v>-0</v>
+        <v>4.85</v>
       </c>
       <c r="N8">
-        <v>-0</v>
+        <v>0.06092964824120603</v>
       </c>
       <c r="O8">
-        <v>-0</v>
+        <v>0.2214611872146119</v>
       </c>
       <c r="P8">
-        <v>-0</v>
+        <v>4.85</v>
       </c>
       <c r="Q8">
-        <v>-0</v>
+        <v>0.06092964824120603</v>
       </c>
       <c r="R8">
-        <v>-0</v>
+        <v>0.2214611872146119</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
       <c r="U8">
-        <v>3.52</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="V8">
-        <v>0.05847176079734219</v>
+        <v>0.1085427135678392</v>
       </c>
       <c r="W8">
-        <v>0.1180602006688963</v>
+        <v>0.2414553472987872</v>
       </c>
       <c r="X8">
-        <v>0.06929075198634665</v>
+        <v>0.08695019649181815</v>
       </c>
       <c r="Y8">
-        <v>0.04876944868254966</v>
+        <v>0.154505150806969</v>
       </c>
       <c r="Z8">
-        <v>0.0982083609820836</v>
+        <v>0.2926391382405745</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.05978712757916416</v>
+        <v>0.09127003681925264</v>
       </c>
       <c r="AC8">
-        <v>-0.05978712757916416</v>
+        <v>-0.09127003681925264</v>
       </c>
       <c r="AD8">
-        <v>154.8</v>
+        <v>104</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>154.8</v>
+        <v>104</v>
       </c>
       <c r="AG8">
-        <v>151.28</v>
+        <v>95.36</v>
       </c>
       <c r="AH8">
-        <v>0.7200000000000001</v>
+        <v>0.5664488017429194</v>
       </c>
       <c r="AI8">
-        <v>0.8449781659388647</v>
+        <v>0.3783193888686796</v>
       </c>
       <c r="AJ8">
-        <v>0.715339512010592</v>
+        <v>0.5450388660265204</v>
       </c>
       <c r="AK8">
-        <v>0.8419412288512912</v>
+        <v>0.3581461729136934</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1439,111 +1421,227 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>Victoria Mutual Investments Limited (JMSE:VMIL)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>1.89</v>
+      </c>
+      <c r="L9">
+        <v>0.1672566371681416</v>
+      </c>
+      <c r="M9">
+        <v>1.53</v>
+      </c>
+      <c r="N9">
+        <v>0.03863636363636364</v>
+      </c>
+      <c r="O9">
+        <v>0.8095238095238095</v>
+      </c>
+      <c r="P9">
+        <v>1.53</v>
+      </c>
+      <c r="Q9">
+        <v>0.03863636363636364</v>
+      </c>
+      <c r="R9">
+        <v>0.8095238095238095</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>1.54</v>
+      </c>
+      <c r="V9">
+        <v>0.03888888888888889</v>
+      </c>
+      <c r="W9">
+        <v>0.06136363636363636</v>
+      </c>
+      <c r="X9">
+        <v>0.1325314659394186</v>
+      </c>
+      <c r="Y9">
+        <v>-0.07116782957578226</v>
+      </c>
+      <c r="Z9">
+        <v>0.06072656921754084</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0.0956443428088391</v>
+      </c>
+      <c r="AC9">
+        <v>-0.0956443428088391</v>
+      </c>
+      <c r="AD9">
+        <v>150.7</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>150.7</v>
+      </c>
+      <c r="AG9">
+        <v>149.16</v>
+      </c>
+      <c r="AH9">
+        <v>0.791907514450867</v>
+      </c>
+      <c r="AI9">
+        <v>0.8833528722157092</v>
+      </c>
+      <c r="AJ9">
+        <v>0.7902097902097902</v>
+      </c>
+      <c r="AK9">
+        <v>0.8822903111321424</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Jamaica</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>Community &amp; Workers of Jamaica Co-operative Credit Union Limited (JMSE:CWJDEFERREDA)</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>1.94</v>
-      </c>
-      <c r="L9">
-        <v>0.1577235772357723</v>
-      </c>
-      <c r="M9">
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>2.02</v>
+      </c>
+      <c r="L10">
+        <v>0.1603174603174603</v>
+      </c>
+      <c r="M10">
         <v>0.095</v>
       </c>
-      <c r="N9">
-        <v>0.05337078651685393</v>
-      </c>
-      <c r="O9">
-        <v>0.04896907216494845</v>
-      </c>
-      <c r="P9">
+      <c r="N10">
+        <v>0.04871794871794872</v>
+      </c>
+      <c r="O10">
+        <v>0.04702970297029703</v>
+      </c>
+      <c r="P10">
         <v>0.095</v>
       </c>
-      <c r="Q9">
-        <v>0.05337078651685393</v>
-      </c>
-      <c r="R9">
-        <v>0.04896907216494845</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>20.6</v>
-      </c>
-      <c r="V9">
-        <v>11.57303370786517</v>
-      </c>
-      <c r="W9">
-        <v>0.1134502923976608</v>
-      </c>
-      <c r="X9">
-        <v>0.3392346541118121</v>
-      </c>
-      <c r="Y9">
-        <v>-0.2257843617141513</v>
-      </c>
-      <c r="Z9">
-        <v>0.3544668587896254</v>
-      </c>
-      <c r="AA9">
-        <v>0</v>
-      </c>
-      <c r="AB9">
-        <v>0.06838983921732798</v>
-      </c>
-      <c r="AC9">
-        <v>-0.06838983921732798</v>
-      </c>
-      <c r="AD9">
-        <v>39.2</v>
-      </c>
-      <c r="AE9">
-        <v>0</v>
-      </c>
-      <c r="AF9">
-        <v>39.2</v>
-      </c>
-      <c r="AG9">
-        <v>18.6</v>
-      </c>
-      <c r="AH9">
-        <v>0.956564177647633</v>
-      </c>
-      <c r="AI9">
-        <v>0.6829268292682926</v>
-      </c>
-      <c r="AJ9">
-        <v>0.9126594700686947</v>
-      </c>
-      <c r="AK9">
-        <v>0.5054347826086957</v>
-      </c>
-      <c r="AL9">
-        <v>0</v>
-      </c>
-      <c r="AM9">
+      <c r="Q10">
+        <v>0.04871794871794872</v>
+      </c>
+      <c r="R10">
+        <v>0.04702970297029703</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>23.2</v>
+      </c>
+      <c r="V10">
+        <v>11.8974358974359</v>
+      </c>
+      <c r="W10">
+        <v>0.110989010989011</v>
+      </c>
+      <c r="X10">
+        <v>0.4232354178904055</v>
+      </c>
+      <c r="Y10">
+        <v>-0.3122464069013945</v>
+      </c>
+      <c r="Z10">
+        <v>0.3423913043478261</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0.1104202607302267</v>
+      </c>
+      <c r="AC10">
+        <v>-0.1104202607302267</v>
+      </c>
+      <c r="AD10">
+        <v>38.5</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>38.5</v>
+      </c>
+      <c r="AG10">
+        <v>15.3</v>
+      </c>
+      <c r="AH10">
+        <v>0.9517923362175524</v>
+      </c>
+      <c r="AI10">
+        <v>0.6615120274914089</v>
+      </c>
+      <c r="AJ10">
+        <v>0.8869565217391304</v>
+      </c>
+      <c r="AK10">
+        <v>0.4371428571428572</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/jamaica/jamaica_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/jamaica/jamaica_financial_svcs_non_bank_insurance.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.206</v>
+        <v>0.07364999999999999</v>
       </c>
       <c r="E2">
-        <v>0.103855</v>
+        <v>-0.00585</v>
       </c>
       <c r="G2">
-        <v>0.04601701469450889</v>
+        <v>0.1288497800125707</v>
       </c>
       <c r="H2">
-        <v>0.04601701469450889</v>
+        <v>0.1288497800125707</v>
       </c>
       <c r="I2">
-        <v>0.04949729311678268</v>
+        <v>0.08249528598365807</v>
       </c>
       <c r="J2">
-        <v>0.04176973318673211</v>
+        <v>0.06418674300965589</v>
       </c>
       <c r="K2">
-        <v>38.522</v>
+        <v>17.507</v>
       </c>
       <c r="L2">
-        <v>0.3724091260634184</v>
+        <v>0.2750942803268385</v>
       </c>
       <c r="M2">
-        <v>11.175</v>
+        <v>4.779</v>
       </c>
       <c r="N2">
-        <v>0.03448541891683381</v>
+        <v>0.01880015735641227</v>
       </c>
       <c r="O2">
-        <v>0.2900939722755828</v>
+        <v>0.2729765236762438</v>
       </c>
       <c r="P2">
-        <v>11.175</v>
+        <v>4.779</v>
       </c>
       <c r="Q2">
-        <v>0.03448541891683381</v>
+        <v>0.01880015735641227</v>
       </c>
       <c r="R2">
-        <v>0.2900939722755828</v>
+        <v>0.2729765236762438</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,70 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>45.795</v>
+        <v>16.211</v>
       </c>
       <c r="V2">
-        <v>0.1413207838296559</v>
+        <v>0.06377261998426435</v>
       </c>
       <c r="W2">
-        <v>0.1707854154213987</v>
+        <v>0.1434192509061619</v>
       </c>
       <c r="X2">
-        <v>0.07825883892266655</v>
+        <v>0.07423804743634685</v>
       </c>
       <c r="Y2">
-        <v>0.09252657649873214</v>
+        <v>0.06918120346981504</v>
       </c>
       <c r="Z2">
-        <v>0.2052018591954992</v>
+        <v>0.1887049809337991</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.08506621525715261</v>
+        <v>0.07501472811131127</v>
       </c>
       <c r="AC2">
-        <v>-0.08506621525715261</v>
+        <v>-0.07406760299736527</v>
       </c>
       <c r="AD2">
-        <v>365.87</v>
+        <v>253.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>365.87</v>
+        <v>253.4</v>
       </c>
       <c r="AG2">
-        <v>320.075</v>
+        <v>237.189</v>
       </c>
       <c r="AH2">
-        <v>0.530307861781076</v>
+        <v>0.4992119779353822</v>
       </c>
       <c r="AI2">
-        <v>0.5468091466148558</v>
+        <v>0.6551358618371727</v>
       </c>
       <c r="AJ2">
-        <v>0.4969144187851737</v>
+        <v>0.4826909027267603</v>
       </c>
       <c r="AK2">
-        <v>0.5135126462967567</v>
+        <v>0.6400497599702087</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.676</v>
       </c>
       <c r="AM2">
-        <v>-0.184</v>
+        <v>0.2650000000000001</v>
       </c>
       <c r="AN2">
-        <v>67.62846580406654</v>
+        <v>43.6144578313253</v>
+      </c>
+      <c r="AO2">
+        <v>7.766272189349112</v>
       </c>
       <c r="AP2">
-        <v>59.16358595194085</v>
+        <v>40.82426850258176</v>
       </c>
       <c r="AQ2">
-        <v>-27.82608695652174</v>
+        <v>19.81132075471698</v>
       </c>
     </row>
     <row r="3">
@@ -719,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.206</v>
+        <v>0.098</v>
       </c>
       <c r="E3">
-        <v>0.257</v>
+        <v>-0.0009</v>
       </c>
       <c r="G3">
-        <v>0.344927536231884</v>
+        <v>0.3976744186046511</v>
       </c>
       <c r="H3">
-        <v>0.344927536231884</v>
+        <v>0.3976744186046511</v>
       </c>
       <c r="I3">
-        <v>0.3710144927536232</v>
+        <v>0.2589147286821705</v>
       </c>
       <c r="J3">
-        <v>0.2480417041949835</v>
+        <v>0.1608723514211886</v>
       </c>
       <c r="K3">
-        <v>3.54</v>
+        <v>2.34</v>
       </c>
       <c r="L3">
-        <v>0.2565217391304347</v>
+        <v>0.1813953488372093</v>
       </c>
       <c r="M3">
-        <v>2.01</v>
+        <v>0.577</v>
       </c>
       <c r="N3">
-        <v>0.02742155525238745</v>
+        <v>0.01279379157427938</v>
       </c>
       <c r="O3">
-        <v>0.5677966101694915</v>
+        <v>0.2465811965811966</v>
       </c>
       <c r="P3">
-        <v>2.01</v>
+        <v>0.577</v>
       </c>
       <c r="Q3">
-        <v>0.02742155525238745</v>
+        <v>0.01279379157427938</v>
       </c>
       <c r="R3">
-        <v>0.5677966101694915</v>
+        <v>0.2465811965811966</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -767,31 +770,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.37</v>
+        <v>0.85</v>
       </c>
       <c r="V3">
-        <v>0.00504774897680764</v>
+        <v>0.0188470066518847</v>
       </c>
       <c r="W3">
-        <v>0.3025641025641026</v>
+        <v>0.18</v>
       </c>
       <c r="X3">
-        <v>0.06311951548698429</v>
+        <v>0.06558478095291721</v>
       </c>
       <c r="Y3">
-        <v>0.2394445870771183</v>
+        <v>0.1144152190470828</v>
       </c>
       <c r="Z3">
-        <v>1.280861332838315</v>
+        <v>1.021377672209026</v>
       </c>
       <c r="AA3">
-        <v>0.3177070278346735</v>
+        <v>0.164311427817366</v>
       </c>
       <c r="AB3">
-        <v>0.06311951548698429</v>
+        <v>0.06558478095291721</v>
       </c>
       <c r="AC3">
-        <v>0.2545875123476892</v>
+        <v>0.09872664686444881</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -803,7 +806,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-0.37</v>
+        <v>-0.85</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -812,25 +815,25 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.005073358014534486</v>
+        <v>-0.0192090395480226</v>
       </c>
       <c r="AK3">
-        <v>-0.02929532858273951</v>
+        <v>-0.05802047781569965</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.184</v>
+        <v>-0.411</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-0.06839186691312384</v>
+        <v>-0.228494623655914</v>
       </c>
       <c r="AQ3">
-        <v>-27.82608695652174</v>
+        <v>-8.126520681265207</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +844,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ISP Finance Services Limited (JMSE:ISP)</t>
+          <t>Lasco Financial Services Limited (JMSE:LASF)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -850,106 +853,121 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0394</v>
+        <v>0.0179</v>
       </c>
       <c r="E4">
-        <v>0.00171</v>
+        <v>-0.146</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.2161971830985915</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>0.2161971830985915</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>0.1345070422535211</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>0.07917325088743844</v>
       </c>
       <c r="K4">
-        <v>0.322</v>
+        <v>0.728</v>
       </c>
       <c r="L4">
-        <v>0.1712765957446809</v>
+        <v>0.05126760563380282</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>0.412</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.02575</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.5659340659340659</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>0.412</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.02575</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.5659340659340659</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>0.515</v>
+        <v>4.66</v>
       </c>
       <c r="V4">
-        <v>0.04256198347107439</v>
+        <v>0.29125</v>
       </c>
       <c r="W4">
-        <v>0.1018987341772152</v>
+        <v>0.052</v>
       </c>
       <c r="X4">
-        <v>0.0659383684184302</v>
+        <v>0.07314311132806853</v>
       </c>
       <c r="Y4">
-        <v>0.03596036575878499</v>
+        <v>-0.02114311132806853</v>
       </c>
       <c r="Z4">
-        <v>0.393964794635373</v>
+        <v>0.7419017763845349</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>0.05873877547552905</v>
       </c>
       <c r="AB4">
-        <v>0.06977180252380108</v>
+        <v>0.07417671444174465</v>
       </c>
       <c r="AC4">
-        <v>-0.06977180252380108</v>
+        <v>-0.0154379389662156</v>
       </c>
       <c r="AD4">
-        <v>1.87</v>
+        <v>6.02</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.87</v>
+        <v>6.02</v>
       </c>
       <c r="AG4">
-        <v>1.355</v>
+        <v>1.359999999999999</v>
       </c>
       <c r="AH4">
-        <v>0.1338582677165354</v>
+        <v>0.2733878292461399</v>
       </c>
       <c r="AI4">
-        <v>0.3568702290076336</v>
+        <v>0.3022088353413654</v>
       </c>
       <c r="AJ4">
-        <v>0.1007060572277964</v>
+        <v>0.07834101382488476</v>
       </c>
       <c r="AK4">
-        <v>0.2867724867724868</v>
+        <v>0.08912188728702486</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>0.676</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>0.676</v>
+      </c>
+      <c r="AN4">
+        <v>2.880382775119617</v>
+      </c>
+      <c r="AO4">
+        <v>2.825443786982248</v>
+      </c>
+      <c r="AP4">
+        <v>0.650717703349282</v>
+      </c>
+      <c r="AQ4">
+        <v>2.825443786982248</v>
       </c>
     </row>
     <row r="5">
@@ -960,7 +978,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Access Financial Services Limited (JMSE:AFS)</t>
+          <t>ISP Finance Services Limited (JMSE:ISP)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -969,10 +987,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0597</v>
+        <v>0.0493</v>
       </c>
       <c r="E5">
-        <v>-0.111</v>
+        <v>-0.0108</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -987,85 +1005,82 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>2.58</v>
+        <v>0.279</v>
       </c>
       <c r="L5">
-        <v>0.2205128205128205</v>
+        <v>0.1438144329896907</v>
       </c>
       <c r="M5">
-        <v>1.18</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.02505307855626327</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>0.4573643410852713</v>
+        <v>-0</v>
       </c>
       <c r="P5">
-        <v>1.18</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.02505307855626327</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>0.4573643410852713</v>
+        <v>-0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>4.81</v>
+        <v>0.296</v>
       </c>
       <c r="V5">
-        <v>0.1021231422505308</v>
+        <v>0.01510204081632653</v>
       </c>
       <c r="W5">
-        <v>0.1474285714285714</v>
+        <v>0.0827893175074184</v>
       </c>
       <c r="X5">
-        <v>0.07074840808401597</v>
+        <v>0.06894654427659969</v>
       </c>
       <c r="Y5">
-        <v>0.07668016334455546</v>
+        <v>0.01384277323081871</v>
       </c>
       <c r="Z5">
-        <v>0.3546529251288269</v>
+        <v>0.4105820105820105</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.07777551842588168</v>
+        <v>0.07088093260207225</v>
       </c>
       <c r="AC5">
-        <v>-0.07777551842588168</v>
+        <v>-0.07088093260207225</v>
       </c>
       <c r="AD5">
-        <v>19.7</v>
+        <v>3.28</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>19.7</v>
+        <v>3.28</v>
       </c>
       <c r="AG5">
-        <v>14.89</v>
+        <v>2.984</v>
       </c>
       <c r="AH5">
-        <v>0.2949101796407186</v>
+        <v>0.1433566433566433</v>
       </c>
       <c r="AI5">
-        <v>0.5143603133159269</v>
+        <v>0.47953216374269</v>
       </c>
       <c r="AJ5">
-        <v>0.2402000322632683</v>
+        <v>0.1321289408430747</v>
       </c>
       <c r="AK5">
-        <v>0.4446103314422216</v>
+        <v>0.4559902200488997</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1082,7 +1097,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Eppley Limited (JMSE:EPLY)</t>
+          <t>Dolla Financial Services Limited (JMSE:DOLLA)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1090,12 +1105,6 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D6">
-        <v>0.381</v>
-      </c>
-      <c r="E6">
-        <v>0.206</v>
-      </c>
       <c r="G6">
         <v>0</v>
       </c>
@@ -1109,28 +1118,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>1.63</v>
+        <v>2.7</v>
       </c>
       <c r="L6">
-        <v>0.5</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="M6">
-        <v>1.51</v>
+        <v>1.28</v>
       </c>
       <c r="N6">
-        <v>0.03087934560327198</v>
+        <v>0.03091787439613527</v>
       </c>
       <c r="O6">
-        <v>0.9263803680981596</v>
+        <v>0.474074074074074</v>
       </c>
       <c r="P6">
-        <v>1.51</v>
+        <v>1.28</v>
       </c>
       <c r="Q6">
-        <v>0.03087934560327198</v>
+        <v>0.03091787439613527</v>
       </c>
       <c r="R6">
-        <v>0.9263803680981596</v>
+        <v>0.474074074074074</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1139,55 +1148,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>3.62</v>
+        <v>0.396</v>
       </c>
       <c r="V6">
-        <v>0.07402862985685071</v>
+        <v>0.009565217391304349</v>
       </c>
       <c r="W6">
-        <v>0.2328571428571428</v>
+        <v>0.5720338983050848</v>
       </c>
       <c r="X6">
-        <v>0.07337697984115711</v>
+        <v>0.07150460572874312</v>
       </c>
       <c r="Y6">
-        <v>0.1594801630159857</v>
+        <v>0.5005292925763416</v>
       </c>
       <c r="Z6">
-        <v>0.1014628073451603</v>
+        <v>0.8004065557108372</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.08100765259514765</v>
+        <v>0.07228246421385265</v>
       </c>
       <c r="AC6">
-        <v>-0.08100765259514765</v>
+        <v>-0.07228246421385265</v>
       </c>
       <c r="AD6">
-        <v>27.5</v>
+        <v>12.2</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>27.5</v>
+        <v>12.2</v>
       </c>
       <c r="AG6">
-        <v>23.88</v>
+        <v>11.804</v>
       </c>
       <c r="AH6">
-        <v>0.3599476439790575</v>
+        <v>0.2276119402985075</v>
       </c>
       <c r="AI6">
-        <v>0.7980266976204294</v>
+        <v>0.6692265496434449</v>
       </c>
       <c r="AJ6">
-        <v>0.3281121187139324</v>
+        <v>0.2218630178182092</v>
       </c>
       <c r="AK6">
-        <v>0.7743190661478599</v>
+        <v>0.6618817988112593</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1204,7 +1213,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sygnus Real Estate Finance Limited (JMSE:SRFJMD)</t>
+          <t>Access Financial Services Limited (JMSE:AFS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1212,80 +1221,104 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D7">
+        <v>0.005430000000000001</v>
+      </c>
+      <c r="E7">
+        <v>-0.159</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
       <c r="K7">
-        <v>4.64</v>
+        <v>2.07</v>
+      </c>
+      <c r="L7">
+        <v>0.2076228686058174</v>
       </c>
       <c r="M7">
-        <v>-0</v>
+        <v>1.08</v>
       </c>
       <c r="N7">
-        <v>-0</v>
+        <v>0.02448979591836735</v>
       </c>
       <c r="O7">
-        <v>-0</v>
+        <v>0.5217391304347827</v>
       </c>
       <c r="P7">
-        <v>-0</v>
+        <v>1.08</v>
       </c>
       <c r="Q7">
-        <v>-0</v>
+        <v>0.02448979591836735</v>
       </c>
       <c r="R7">
-        <v>-0</v>
+        <v>0.5217391304347827</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
       <c r="U7">
-        <v>3.1</v>
+        <v>3.82</v>
       </c>
       <c r="V7">
-        <v>0.1441860465116279</v>
+        <v>0.08662131519274376</v>
       </c>
       <c r="W7">
-        <v>0.1941422594142259</v>
+        <v>0.1083769633507853</v>
       </c>
       <c r="X7">
-        <v>0.08314069800417601</v>
+        <v>0.07533298354462517</v>
       </c>
       <c r="Y7">
-        <v>0.1110015614100499</v>
+        <v>0.03304397980616015</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>0.298145933014354</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.08912477791915754</v>
+        <v>0.07585274178087789</v>
       </c>
       <c r="AC7">
-        <v>-0.08912477791915754</v>
+        <v>-0.07585274178087789</v>
       </c>
       <c r="AD7">
-        <v>23.6</v>
+        <v>21.4</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>23.6</v>
+        <v>21.4</v>
       </c>
       <c r="AG7">
-        <v>20.5</v>
+        <v>17.58</v>
       </c>
       <c r="AH7">
-        <v>0.5232815964523282</v>
+        <v>0.3267175572519084</v>
       </c>
       <c r="AI7">
-        <v>0.3172043010752688</v>
+        <v>0.5417721518987342</v>
       </c>
       <c r="AJ7">
-        <v>0.4880952380952381</v>
+        <v>0.2850194552529183</v>
       </c>
       <c r="AK7">
-        <v>0.2875175315568023</v>
+        <v>0.4927130044843049</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1302,7 +1335,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mayberry Investments Limited (JMSE:MIL)</t>
+          <t>Eppley Limited (JMSE:EPLY)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1311,7 +1344,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.596</v>
+        <v>0.245</v>
+      </c>
+      <c r="E8">
+        <v>0.382</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1326,28 +1362,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>21.9</v>
+        <v>3.18</v>
       </c>
       <c r="L8">
-        <v>0.4478527607361963</v>
+        <v>0.8091603053435115</v>
       </c>
       <c r="M8">
-        <v>4.85</v>
+        <v>1.43</v>
       </c>
       <c r="N8">
-        <v>0.06092964824120603</v>
+        <v>0.03213483146067415</v>
       </c>
       <c r="O8">
-        <v>0.2214611872146119</v>
+        <v>0.4496855345911949</v>
       </c>
       <c r="P8">
-        <v>4.85</v>
+        <v>1.43</v>
       </c>
       <c r="Q8">
-        <v>0.06092964824120603</v>
+        <v>0.03213483146067415</v>
       </c>
       <c r="R8">
-        <v>0.2214611872146119</v>
+        <v>0.4496855345911949</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1356,55 +1392,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>8.640000000000001</v>
+        <v>2.55</v>
       </c>
       <c r="V8">
-        <v>0.1085427135678392</v>
+        <v>0.05730337078651685</v>
       </c>
       <c r="W8">
-        <v>0.2414553472987872</v>
+        <v>0.456896551724138</v>
       </c>
       <c r="X8">
-        <v>0.08695019649181815</v>
+        <v>0.07750250371399049</v>
       </c>
       <c r="Y8">
-        <v>0.154505150806969</v>
+        <v>0.3793940480101475</v>
       </c>
       <c r="Z8">
-        <v>0.2926391382405745</v>
+        <v>0.127431906614786</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.09127003681925264</v>
+        <v>0.07728703229000486</v>
       </c>
       <c r="AC8">
-        <v>-0.09127003681925264</v>
+        <v>-0.07728703229000486</v>
       </c>
       <c r="AD8">
-        <v>104</v>
+        <v>26.4</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>104</v>
+        <v>26.4</v>
       </c>
       <c r="AG8">
-        <v>95.36</v>
+        <v>23.85</v>
       </c>
       <c r="AH8">
-        <v>0.5664488017429194</v>
+        <v>0.3723554301833568</v>
       </c>
       <c r="AI8">
-        <v>0.3783193888686796</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="AJ8">
-        <v>0.5450388660265204</v>
+        <v>0.3489392831016825</v>
       </c>
       <c r="AK8">
-        <v>0.3581461729136934</v>
+        <v>0.6437246963562753</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1421,7 +1457,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Victoria Mutual Investments Limited (JMSE:VMIL)</t>
+          <t>Sygnus Real Estate Finance Limited (JMSE:SRFJMD)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1429,98 +1465,80 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
       <c r="K9">
-        <v>1.89</v>
-      </c>
-      <c r="L9">
-        <v>0.1672566371681416</v>
+        <v>2.73</v>
       </c>
       <c r="M9">
-        <v>1.53</v>
+        <v>-0</v>
       </c>
       <c r="N9">
-        <v>0.03863636363636364</v>
+        <v>-0</v>
       </c>
       <c r="O9">
-        <v>0.8095238095238095</v>
+        <v>-0</v>
       </c>
       <c r="P9">
-        <v>1.53</v>
+        <v>-0</v>
       </c>
       <c r="Q9">
-        <v>0.03863636363636364</v>
+        <v>-0</v>
       </c>
       <c r="R9">
-        <v>0.8095238095238095</v>
+        <v>-0</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
       <c r="U9">
-        <v>1.54</v>
+        <v>0.669</v>
       </c>
       <c r="V9">
-        <v>0.03888888888888889</v>
+        <v>0.03935294117647059</v>
       </c>
       <c r="W9">
-        <v>0.06136363636363636</v>
+        <v>0.06247139588100686</v>
       </c>
       <c r="X9">
-        <v>0.1325314659394186</v>
+        <v>0.09997171297041241</v>
       </c>
       <c r="Y9">
-        <v>-0.07116782957578226</v>
+        <v>-0.03750031708940554</v>
       </c>
       <c r="Z9">
-        <v>0.06072656921754084</v>
+        <v>0</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.0956443428088391</v>
+        <v>0.08542305080120968</v>
       </c>
       <c r="AC9">
-        <v>-0.0956443428088391</v>
+        <v>-0.08542305080120968</v>
       </c>
       <c r="AD9">
-        <v>150.7</v>
+        <v>29.1</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>150.7</v>
+        <v>29.1</v>
       </c>
       <c r="AG9">
-        <v>149.16</v>
+        <v>28.431</v>
       </c>
       <c r="AH9">
-        <v>0.791907514450867</v>
+        <v>0.631236442516269</v>
       </c>
       <c r="AI9">
-        <v>0.8833528722157092</v>
+        <v>0.3890374331550802</v>
       </c>
       <c r="AJ9">
-        <v>0.7902097902097902</v>
+        <v>0.6258061675948142</v>
       </c>
       <c r="AK9">
-        <v>0.8822903111321424</v>
+        <v>0.3835237619889115</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1537,7 +1555,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Community &amp; Workers of Jamaica Co-operative Credit Union Limited (JMSE:CWJDEFERREDA)</t>
+          <t>Victoria Mutual Investments Limited (JMSE:VMIL)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1545,6 +1563,12 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D10">
+        <v>0.167</v>
+      </c>
+      <c r="E10">
+        <v>0.115</v>
+      </c>
       <c r="G10">
         <v>0</v>
       </c>
@@ -1558,85 +1582,82 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>2.02</v>
+        <v>3.48</v>
       </c>
       <c r="L10">
-        <v>0.1603174603174603</v>
+        <v>0.2416666666666667</v>
       </c>
       <c r="M10">
-        <v>0.095</v>
+        <v>-0</v>
       </c>
       <c r="N10">
-        <v>0.04871794871794872</v>
+        <v>-0</v>
       </c>
       <c r="O10">
-        <v>0.04702970297029703</v>
+        <v>-0</v>
       </c>
       <c r="P10">
-        <v>0.095</v>
+        <v>-0</v>
       </c>
       <c r="Q10">
-        <v>0.04871794871794872</v>
+        <v>-0</v>
       </c>
       <c r="R10">
-        <v>0.04702970297029703</v>
+        <v>-0</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
       <c r="U10">
-        <v>23.2</v>
+        <v>2.97</v>
       </c>
       <c r="V10">
-        <v>11.8974358974359</v>
+        <v>0.1120754716981132</v>
       </c>
       <c r="W10">
-        <v>0.110989010989011</v>
+        <v>0.1784615384615384</v>
       </c>
       <c r="X10">
-        <v>0.4232354178904055</v>
+        <v>0.1830840558878842</v>
       </c>
       <c r="Y10">
-        <v>-0.3122464069013945</v>
+        <v>-0.004622517426345785</v>
       </c>
       <c r="Z10">
-        <v>0.3423913043478261</v>
+        <v>0.08537886872998933</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.1104202607302267</v>
+        <v>0.09242380989292154</v>
       </c>
       <c r="AC10">
-        <v>-0.1104202607302267</v>
+        <v>-0.09242380989292154</v>
       </c>
       <c r="AD10">
-        <v>38.5</v>
+        <v>155</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>38.5</v>
+        <v>155</v>
       </c>
       <c r="AG10">
-        <v>15.3</v>
+        <v>152.03</v>
       </c>
       <c r="AH10">
-        <v>0.9517923362175524</v>
+        <v>0.8539944903581267</v>
       </c>
       <c r="AI10">
-        <v>0.6615120274914089</v>
+        <v>0.8990719257540603</v>
       </c>
       <c r="AJ10">
-        <v>0.8869565217391304</v>
+        <v>0.8515655632106649</v>
       </c>
       <c r="AK10">
-        <v>0.4371428571428572</v>
+        <v>0.8973027208876821</v>
       </c>
       <c r="AL10">
         <v>0</v>
